--- a/risk_matrix/risk_matrix_2023.xlsx
+++ b/risk_matrix/risk_matrix_2023.xlsx
@@ -505,7 +505,7 @@
       <c r="D2" s="3" t="inlineStr"/>
       <c r="E2" s="3" t="inlineStr"/>
       <c r="F2" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G2" s="3" t="inlineStr"/>
     </row>
@@ -516,17 +516,17 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" s="3" t="inlineStr"/>
       <c r="D3" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
     </row>
@@ -537,19 +537,19 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G4" s="3" t="inlineStr"/>
     </row>
@@ -578,9 +578,7 @@
       <c r="E6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="F6" s="3" t="inlineStr"/>
       <c r="G6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
@@ -594,13 +592,13 @@
         <v>1</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>12</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
     </row>

--- a/risk_matrix/risk_matrix_2023.xlsx
+++ b/risk_matrix/risk_matrix_2023.xlsx
@@ -505,7 +505,7 @@
       <c r="D2" s="3" t="inlineStr"/>
       <c r="E2" s="3" t="inlineStr"/>
       <c r="F2" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G2" s="3" t="inlineStr"/>
     </row>
@@ -516,17 +516,17 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="3" t="inlineStr"/>
       <c r="D3" s="4" t="n">
         <v>4</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
     </row>
@@ -543,10 +543,10 @@
         <v>1</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F4" s="4" t="n">
         <v>12</v>
@@ -598,7 +598,7 @@
         <v>12</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
     </row>

--- a/risk_matrix/risk_matrix_2023.xlsx
+++ b/risk_matrix/risk_matrix_2023.xlsx
@@ -503,9 +503,11 @@
       <c r="B2" s="3" t="inlineStr"/>
       <c r="C2" s="3" t="inlineStr"/>
       <c r="D2" s="3" t="inlineStr"/>
-      <c r="E2" s="3" t="inlineStr"/>
+      <c r="E2" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="F2" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G2" s="3" t="inlineStr"/>
     </row>
@@ -516,17 +518,17 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" s="3" t="inlineStr"/>
       <c r="D3" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
     </row>
@@ -539,17 +541,15 @@
       <c r="B4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="C4" s="3" t="inlineStr"/>
       <c r="D4" s="4" t="n">
         <v>10</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G4" s="3" t="inlineStr"/>
     </row>
@@ -578,7 +578,9 @@
       <c r="E6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="3" t="inlineStr"/>
+      <c r="F6" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="G6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
@@ -598,7 +600,7 @@
         <v>12</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
     </row>

--- a/risk_matrix/risk_matrix_2023.xlsx
+++ b/risk_matrix/risk_matrix_2023.xlsx
@@ -525,7 +525,7 @@
         <v>8</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F3" s="4" t="n">
         <v>14</v>
@@ -546,7 +546,7 @@
         <v>10</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F4" s="4" t="n">
         <v>13</v>

--- a/risk_matrix/risk_matrix_2023.xlsx
+++ b/risk_matrix/risk_matrix_2023.xlsx
@@ -507,7 +507,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G2" s="3" t="inlineStr"/>
     </row>
@@ -525,10 +525,10 @@
         <v>8</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
     </row>
@@ -543,13 +543,13 @@
       </c>
       <c r="C4" s="3" t="inlineStr"/>
       <c r="D4" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="F4" s="4" t="n">
         <v>10</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>13</v>
       </c>
       <c r="G4" s="3" t="inlineStr"/>
     </row>
@@ -573,14 +573,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr"/>
-      <c r="C6" s="3" t="inlineStr"/>
+      <c r="C6" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="D6" s="3" t="inlineStr"/>
       <c r="E6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="F6" s="3" t="inlineStr"/>
       <c r="G6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
@@ -590,14 +590,12 @@
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr"/>
-      <c r="C7" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="4" t="n">
         <v>2</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F7" s="4" t="n">
         <v>2</v>

--- a/risk_matrix/risk_matrix_2023.xlsx
+++ b/risk_matrix/risk_matrix_2023.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Risk Matrix" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Matrix" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,11 +27,11 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -68,10 +68,10 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -504,10 +504,10 @@
       <c r="C2" s="3" t="inlineStr"/>
       <c r="D2" s="3" t="inlineStr"/>
       <c r="E2" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G2" s="3" t="inlineStr"/>
     </row>
@@ -518,17 +518,17 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C3" s="3" t="inlineStr"/>
       <c r="D3" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
     </row>
@@ -543,13 +543,13 @@
       </c>
       <c r="C4" s="3" t="inlineStr"/>
       <c r="D4" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="F4" s="4" t="n">
         <v>12</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>10</v>
       </c>
       <c r="G4" s="3" t="inlineStr"/>
     </row>
@@ -573,14 +573,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr"/>
-      <c r="C6" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="C6" s="3" t="inlineStr"/>
       <c r="D6" s="3" t="inlineStr"/>
       <c r="E6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="3" t="inlineStr"/>
+      <c r="F6" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="G6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
@@ -590,15 +590,17 @@
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr"/>
-      <c r="C7" s="3" t="inlineStr"/>
+      <c r="C7" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="D7" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
     </row>
